--- a/artfynd/A 38511-2025 artfynd.xlsx
+++ b/artfynd/A 38511-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136483053</v>
       </c>
       <c r="B2" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 38511-2025 artfynd.xlsx
+++ b/artfynd/A 38511-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136483053</v>
       </c>
       <c r="B2" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 38511-2025 artfynd.xlsx
+++ b/artfynd/A 38511-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136483053</v>
       </c>
       <c r="B2" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 38511-2025 artfynd.xlsx
+++ b/artfynd/A 38511-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136483053</v>
       </c>
       <c r="B2" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 38511-2025 artfynd.xlsx
+++ b/artfynd/A 38511-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136483053</v>
       </c>
       <c r="B2" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Camilla Carlsson, Per-Anders Jonsson</t>
+          <t>Per-Anders Jonsson, Camilla Carlsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 38511-2025 artfynd.xlsx
+++ b/artfynd/A 38511-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136483053</v>
       </c>
       <c r="B2" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Per-Anders Jonsson, Camilla Carlsson</t>
+          <t>Camilla Carlsson, Per-Anders Jonsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 38511-2025 artfynd.xlsx
+++ b/artfynd/A 38511-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136483053</v>
       </c>
       <c r="B2" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 38511-2025 artfynd.xlsx
+++ b/artfynd/A 38511-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136483053</v>
       </c>
       <c r="B2" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 38511-2025 artfynd.xlsx
+++ b/artfynd/A 38511-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136483053</v>
       </c>
       <c r="B2" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
